--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/OHIO_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/OHIO_2010.xlsx
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C105">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C361">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C405">
